--- a/CALTEC.xlsx
+++ b/CALTEC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edison\Desktop\CALTEC\Codigo CATLEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4E84F50-EEF1-467D-964A-8859A2AB9247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5208EC48-6F32-49E7-BC4B-A4FDF49081D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{AFBC47FB-AA6E-4273-9F80-1754DD486B9C}"/>
+    <workbookView xWindow="3108" yWindow="0" windowWidth="8748" windowHeight="13680" activeTab="1" xr2:uid="{AFBC47FB-AA6E-4273-9F80-1754DD486B9C}"/>
   </bookViews>
   <sheets>
     <sheet name="TD BD" sheetId="3" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4894" uniqueCount="1890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4892" uniqueCount="1889">
   <si>
     <t>Código proyecto</t>
   </si>
@@ -5872,9 +5872,6 @@
   </si>
   <si>
     <t>160</t>
-  </si>
-  <si>
-    <t>161</t>
   </si>
   <si>
     <t>162</t>
@@ -17554,7 +17551,7 @@
     <row r="2" spans="1:36" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <f t="shared" ref="A2:A33" si="0">MAX($B$2:$B$128)</f>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B2" cm="1">
         <f t="array" ref="B2">IFERROR(MAX(--_xlfn.TEXTSPLIT(C2,";")),0)</f>
@@ -17658,14 +17655,14 @@
         <v>0</v>
       </c>
       <c r="AJ2" s="71" t="str">
-        <f>MID(D2,5,LEN(D2)-4)</f>
+        <f t="shared" ref="AJ2:AJ33" si="1">MID(D2,5,LEN(D2)-4)</f>
         <v>EIMQ1</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B3" cm="1">
         <f t="array" ref="B3">IFERROR(MAX(--_xlfn.TEXTSPLIT(C3,";")),0)</f>
@@ -17771,14 +17768,14 @@
         <v>0</v>
       </c>
       <c r="AJ3" s="71" t="str">
-        <f>MID(D3,5,LEN(D3)-4)</f>
+        <f t="shared" si="1"/>
         <v>PBCH1</v>
       </c>
     </row>
     <row r="4" spans="1:36" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B4" cm="1">
         <f t="array" ref="B4">IFERROR(MAX(--_xlfn.TEXTSPLIT(C4,";")),0)</f>
@@ -17838,14 +17835,14 @@
       <c r="AH4" s="22"/>
       <c r="AI4" s="23"/>
       <c r="AJ4" s="71" t="str">
-        <f>MID(D4,5,LEN(D4)-4)</f>
+        <f t="shared" si="1"/>
         <v>PDRC1</v>
       </c>
     </row>
     <row r="5" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B5" cm="1">
         <f t="array" ref="B5">IFERROR(MAX(--_xlfn.TEXTSPLIT(C5,";")),0)</f>
@@ -17951,14 +17948,14 @@
         <v>1</v>
       </c>
       <c r="AJ5" s="71" t="str">
-        <f>MID(D5,5,LEN(D5)-4)</f>
+        <f t="shared" si="1"/>
         <v>160R1</v>
       </c>
     </row>
     <row r="6" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B6" cm="1">
         <f t="array" ref="B6">IFERROR(MAX(--_xlfn.TEXTSPLIT(C6,";")),0)</f>
@@ -17971,7 +17968,7 @@
         <v>674</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="F6" s="1">
         <v>1</v>
@@ -18064,14 +18061,14 @@
         <v>1</v>
       </c>
       <c r="AJ6" s="71" t="str">
-        <f>MID(D6,5,LEN(D6)-4)</f>
+        <f t="shared" si="1"/>
         <v>1AVO1</v>
       </c>
     </row>
     <row r="7" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B7" cm="1">
         <f t="array" ref="B7">IFERROR(MAX(--_xlfn.TEXTSPLIT(C7,";")),0)</f>
@@ -18084,7 +18081,7 @@
         <v>816</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="F7" s="1">
         <v>1</v>
@@ -18177,14 +18174,14 @@
         <v>0</v>
       </c>
       <c r="AJ7" s="71" t="str">
-        <f>MID(D7,5,LEN(D7)-4)</f>
+        <f t="shared" si="1"/>
         <v>21RG1</v>
       </c>
     </row>
     <row r="8" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B8" cm="1">
         <f t="array" ref="B8">IFERROR(MAX(--_xlfn.TEXTSPLIT(C8,";")),0)</f>
@@ -18197,7 +18194,7 @@
         <v>753</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="F8" s="1">
         <v>1</v>
@@ -18290,14 +18287,14 @@
         <v>0.2641</v>
       </c>
       <c r="AJ8" s="71" t="str">
-        <f>MID(D8,5,LEN(D8)-4)</f>
+        <f t="shared" si="1"/>
         <v>2AVO1</v>
       </c>
     </row>
     <row r="9" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B9" cm="1">
         <f t="array" ref="B9">IFERROR(MAX(--_xlfn.TEXTSPLIT(C9,";")),0)</f>
@@ -18310,7 +18307,7 @@
         <v>615</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="F9" s="1">
         <v>1</v>
@@ -18403,14 +18400,14 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="71" t="str">
-        <f>MID(D9,5,LEN(D9)-4)</f>
+        <f t="shared" si="1"/>
         <v>43RU1</v>
       </c>
     </row>
     <row r="10" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B10" cm="1">
         <f t="array" ref="B10">IFERROR(MAX(--_xlfn.TEXTSPLIT(C10,";")),0)</f>
@@ -18516,14 +18513,14 @@
         <v>0</v>
       </c>
       <c r="AJ10" s="71" t="str">
-        <f>MID(D10,5,LEN(D10)-4)</f>
+        <f t="shared" si="1"/>
         <v>60GR1</v>
       </c>
     </row>
     <row r="11" spans="1:36" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B11" cm="1">
         <f t="array" ref="B11">IFERROR(MAX(--_xlfn.TEXTSPLIT(C11,";")),0)</f>
@@ -18629,14 +18626,14 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="71" t="str">
-        <f>MID(D11,5,LEN(D11)-4)</f>
+        <f t="shared" si="1"/>
         <v>60RU1</v>
       </c>
     </row>
     <row r="12" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B12" cm="1">
         <f t="array" ref="B12">IFERROR(MAX(--_xlfn.TEXTSPLIT(C12,";")),0)</f>
@@ -18742,14 +18739,14 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="71" t="str">
-        <f>MID(D12,5,LEN(D12)-4)</f>
+        <f t="shared" si="1"/>
         <v>66RF1</v>
       </c>
     </row>
     <row r="13" spans="1:36" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B13" cm="1">
         <f t="array" ref="B13">IFERROR(MAX(--_xlfn.TEXTSPLIT(C13,";")),0)</f>
@@ -18855,14 +18852,14 @@
         <v>807</v>
       </c>
       <c r="AJ13" s="71" t="str">
-        <f>MID(D13,5,LEN(D13)-4)</f>
+        <f t="shared" si="1"/>
         <v>66RF2</v>
       </c>
     </row>
     <row r="14" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B14" cm="1">
         <f t="array" ref="B14">IFERROR(MAX(--_xlfn.TEXTSPLIT(C14,";")),0)</f>
@@ -18968,14 +18965,14 @@
         <v>2.8500000000000001E-2</v>
       </c>
       <c r="AJ14" s="71" t="str">
-        <f>MID(D14,5,LEN(D14)-4)</f>
+        <f t="shared" si="1"/>
         <v>67CV1</v>
       </c>
     </row>
     <row r="15" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B15" cm="1">
         <f t="array" ref="B15">IFERROR(MAX(--_xlfn.TEXTSPLIT(C15,";")),0)</f>
@@ -19081,14 +19078,14 @@
         <v>1</v>
       </c>
       <c r="AJ15" s="71" t="str">
-        <f>MID(D15,5,LEN(D15)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACIQ1</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B16" cm="1">
         <f t="array" ref="B16">IFERROR(MAX(--_xlfn.TEXTSPLIT(C16,";")),0)</f>
@@ -19194,14 +19191,14 @@
         <v>1</v>
       </c>
       <c r="AJ16" s="71" t="str">
-        <f>MID(D16,5,LEN(D16)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACNO1</v>
       </c>
     </row>
     <row r="17" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B17" cm="1">
         <f t="array" ref="B17">IFERROR(MAX(--_xlfn.TEXTSPLIT(C17,";")),0)</f>
@@ -19214,7 +19211,7 @@
         <v>80</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F17" s="1">
         <v>1</v>
@@ -19307,14 +19304,14 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="71" t="str">
-        <f>MID(D17,5,LEN(D17)-4)</f>
+        <f t="shared" si="1"/>
         <v>ANCO1</v>
       </c>
     </row>
     <row r="18" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" cm="1">
         <f t="array" ref="B18">IFERROR(MAX(--_xlfn.TEXTSPLIT(C18,";")),0)</f>
@@ -19420,14 +19417,14 @@
         <v>1</v>
       </c>
       <c r="AJ18" s="71" t="str">
-        <f>MID(D18,5,LEN(D18)-4)</f>
+        <f t="shared" si="1"/>
         <v>AAMB1</v>
       </c>
     </row>
     <row r="19" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B19" cm="1">
         <f t="array" ref="B19">IFERROR(MAX(--_xlfn.TEXTSPLIT(C19,";")),0)</f>
@@ -19533,14 +19530,14 @@
         <v>0.99839999999999995</v>
       </c>
       <c r="AJ19" s="71" t="str">
-        <f>MID(D19,5,LEN(D19)-4)</f>
+        <f t="shared" si="1"/>
         <v>AAMB2</v>
       </c>
     </row>
     <row r="20" spans="1:36" ht="244.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B20" cm="1">
         <f t="array" ref="B20">IFERROR(MAX(--_xlfn.TEXTSPLIT(C20,";")),0)</f>
@@ -19553,7 +19550,7 @@
         <v>398</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -19646,14 +19643,14 @@
         <v>1</v>
       </c>
       <c r="AJ20" s="71" t="str">
-        <f>MID(D20,5,LEN(D20)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACHA1</v>
       </c>
     </row>
     <row r="21" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" cm="1">
         <f t="array" ref="B21">IFERROR(MAX(--_xlfn.TEXTSPLIT(C21,";")),0)</f>
@@ -19666,7 +19663,7 @@
         <v>832</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="F21" s="1">
         <v>2</v>
@@ -19759,14 +19756,14 @@
         <v>1</v>
       </c>
       <c r="AJ21" s="71" t="str">
-        <f>MID(D21,5,LEN(D21)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACHA2</v>
       </c>
     </row>
     <row r="22" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B22" cm="1">
         <f t="array" ref="B22">IFERROR(MAX(--_xlfn.TEXTSPLIT(C22,";")),0)</f>
@@ -19872,14 +19869,14 @@
         <v>1</v>
       </c>
       <c r="AJ22" s="71" t="str">
-        <f>MID(D22,5,LEN(D22)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACIP1</v>
       </c>
     </row>
     <row r="23" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B23" cm="1">
         <f t="array" ref="B23">IFERROR(MAX(--_xlfn.TEXTSPLIT(C23,";")),0)</f>
@@ -19985,14 +19982,14 @@
         <v>1</v>
       </c>
       <c r="AJ23" s="71" t="str">
-        <f>MID(D23,5,LEN(D23)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACIP2</v>
       </c>
     </row>
     <row r="24" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B24" cm="1">
         <f t="array" ref="B24">IFERROR(MAX(--_xlfn.TEXTSPLIT(C24,";")),0)</f>
@@ -20005,7 +20002,7 @@
         <v>983</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="F24" s="1">
         <v>2</v>
@@ -20098,14 +20095,14 @@
         <v>0</v>
       </c>
       <c r="AJ24" s="71" t="str">
-        <f>MID(D24,5,LEN(D24)-4)</f>
+        <f t="shared" si="1"/>
         <v>ANCO2</v>
       </c>
     </row>
     <row r="25" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B25" cm="1">
         <f t="array" ref="B25">IFERROR(MAX(--_xlfn.TEXTSPLIT(C25,";")),0)</f>
@@ -20211,14 +20208,14 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="71" t="str">
-        <f>MID(D25,5,LEN(D25)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACMA1</v>
       </c>
     </row>
     <row r="26" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B26" cm="1">
         <f t="array" ref="B26">IFERROR(MAX(--_xlfn.TEXTSPLIT(C26,";")),0)</f>
@@ -20324,14 +20321,14 @@
         <v>1</v>
       </c>
       <c r="AJ26" s="71" t="str">
-        <f>MID(D26,5,LEN(D26)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACMA2</v>
       </c>
     </row>
     <row r="27" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B27" cm="1">
         <f t="array" ref="B27">IFERROR(MAX(--_xlfn.TEXTSPLIT(C27,";")),0)</f>
@@ -20344,7 +20341,7 @@
         <v>577</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="F27" s="1">
         <v>1</v>
@@ -20437,14 +20434,14 @@
         <v>1</v>
       </c>
       <c r="AJ27" s="71" t="str">
-        <f>MID(D27,5,LEN(D27)-4)</f>
+        <f t="shared" si="1"/>
         <v>AURA1</v>
       </c>
     </row>
     <row r="28" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B28" cm="1">
         <f t="array" ref="B28">IFERROR(MAX(--_xlfn.TEXTSPLIT(C28,";")),0)</f>
@@ -20550,14 +20547,14 @@
         <v>1</v>
       </c>
       <c r="AJ28" s="71" t="str">
-        <f>MID(D28,5,LEN(D28)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACSU1</v>
       </c>
     </row>
     <row r="29" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B29" cm="1">
         <f t="array" ref="B29">IFERROR(MAX(--_xlfn.TEXTSPLIT(C29,";")),0)</f>
@@ -20663,14 +20660,14 @@
         <v>1</v>
       </c>
       <c r="AJ29" s="71" t="str">
-        <f>MID(D29,5,LEN(D29)-4)</f>
+        <f t="shared" si="1"/>
         <v>ACSU2</v>
       </c>
     </row>
     <row r="30" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B30" cm="1">
         <f t="array" ref="B30">IFERROR(MAX(--_xlfn.TEXTSPLIT(C30,";")),0)</f>
@@ -20776,14 +20773,14 @@
         <v>1</v>
       </c>
       <c r="AJ30" s="71" t="str">
-        <f>MID(D30,5,LEN(D30)-4)</f>
+        <f t="shared" si="1"/>
         <v>ADAI1</v>
       </c>
     </row>
     <row r="31" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B31" cm="1">
         <f t="array" ref="B31">IFERROR(MAX(--_xlfn.TEXTSPLIT(C31,";")),0)</f>
@@ -20889,14 +20886,14 @@
         <v>1</v>
       </c>
       <c r="AJ31" s="71" t="str">
-        <f>MID(D31,5,LEN(D31)-4)</f>
+        <f t="shared" si="1"/>
         <v>ADAI2</v>
       </c>
     </row>
     <row r="32" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B32" cm="1">
         <f t="array" ref="B32">IFERROR(MAX(--_xlfn.TEXTSPLIT(C32,";")),0)</f>
@@ -21002,14 +20999,14 @@
         <v>1</v>
       </c>
       <c r="AJ32" s="71" t="str">
-        <f>MID(D32,5,LEN(D32)-4)</f>
+        <f t="shared" si="1"/>
         <v>ADAI3</v>
       </c>
     </row>
     <row r="33" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B33" cm="1">
         <f t="array" ref="B33">IFERROR(MAX(--_xlfn.TEXTSPLIT(C33,";")),0)</f>
@@ -21115,14 +21112,14 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="71" t="str">
-        <f>MID(D33,5,LEN(D33)-4)</f>
+        <f t="shared" si="1"/>
         <v>ADAI4</v>
       </c>
     </row>
     <row r="34" spans="1:36" ht="147.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
-        <f t="shared" ref="A34:A65" si="1">MAX($B$2:$B$128)</f>
-        <v>188</v>
+        <f t="shared" ref="A34:A65" si="2">MAX($B$2:$B$128)</f>
+        <v>189</v>
       </c>
       <c r="B34" cm="1">
         <f t="array" ref="B34">IFERROR(MAX(--_xlfn.TEXTSPLIT(C34,";")),0)</f>
@@ -21135,7 +21132,7 @@
         <v>180</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
@@ -21228,14 +21225,14 @@
         <v>1</v>
       </c>
       <c r="AJ34" s="71" t="str">
-        <f>MID(D34,5,LEN(D34)-4)</f>
+        <f t="shared" ref="AJ34:AJ65" si="3">MID(D34,5,LEN(D34)-4)</f>
         <v>ALFS1</v>
       </c>
     </row>
     <row r="35" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B35" cm="1">
         <f t="array" ref="B35">IFERROR(MAX(--_xlfn.TEXTSPLIT(C35,";")),0)</f>
@@ -21248,7 +21245,7 @@
         <v>643</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="F35" s="1">
         <v>2</v>
@@ -21341,14 +21338,14 @@
         <v>1</v>
       </c>
       <c r="AJ35" s="71" t="str">
-        <f>MID(D35,5,LEN(D35)-4)</f>
+        <f t="shared" si="3"/>
         <v>ALFS2</v>
       </c>
     </row>
     <row r="36" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B36" cm="1">
         <f t="array" ref="B36">IFERROR(MAX(--_xlfn.TEXTSPLIT(C36,";")),0)</f>
@@ -21361,7 +21358,7 @@
         <v>856</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="F36" s="1">
         <v>3</v>
@@ -21454,14 +21451,14 @@
         <v>0.13500000000000001</v>
       </c>
       <c r="AJ36" s="71" t="str">
-        <f>MID(D36,5,LEN(D36)-4)</f>
+        <f t="shared" si="3"/>
         <v>ALFS3</v>
       </c>
     </row>
     <row r="37" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B37" cm="1">
         <f t="array" ref="B37">IFERROR(MAX(--_xlfn.TEXTSPLIT(C37,";")),0)</f>
@@ -21567,14 +21564,14 @@
         <v>1</v>
       </c>
       <c r="AJ37" s="71" t="str">
-        <f>MID(D37,5,LEN(D37)-4)</f>
+        <f t="shared" si="3"/>
         <v>ALOA1</v>
       </c>
     </row>
     <row r="38" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B38" cm="1">
         <f t="array" ref="B38">IFERROR(MAX(--_xlfn.TEXTSPLIT(C38,";")),0)</f>
@@ -21680,14 +21677,14 @@
         <v>1</v>
       </c>
       <c r="AJ38" s="71" t="str">
-        <f>MID(D38,5,LEN(D38)-4)</f>
+        <f t="shared" si="3"/>
         <v>ALOA2</v>
       </c>
     </row>
     <row r="39" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B39" cm="1">
         <f t="array" ref="B39">IFERROR(MAX(--_xlfn.TEXTSPLIT(C39,";")),0)</f>
@@ -21793,14 +21790,14 @@
         <v>0</v>
       </c>
       <c r="AJ39" s="71" t="str">
-        <f>MID(D39,5,LEN(D39)-4)</f>
+        <f t="shared" si="3"/>
         <v>ALOA3</v>
       </c>
     </row>
     <row r="40" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B40" cm="1">
         <f t="array" ref="B40">IFERROR(MAX(--_xlfn.TEXTSPLIT(C40,";")),0)</f>
@@ -21906,14 +21903,14 @@
         <v>1</v>
       </c>
       <c r="AJ40" s="71" t="str">
-        <f>MID(D40,5,LEN(D40)-4)</f>
+        <f t="shared" si="3"/>
         <v>AVAM1</v>
       </c>
     </row>
     <row r="41" spans="1:36" ht="180" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B41" cm="1">
         <f t="array" ref="B41">IFERROR(MAX(--_xlfn.TEXTSPLIT(C41,";")),0)</f>
@@ -22019,14 +22016,14 @@
         <v>1</v>
       </c>
       <c r="AJ41" s="71" t="str">
-        <f>MID(D41,5,LEN(D41)-4)</f>
+        <f t="shared" si="3"/>
         <v>AVAM2</v>
       </c>
     </row>
     <row r="42" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B42" cm="1">
         <f t="array" ref="B42">IFERROR(MAX(--_xlfn.TEXTSPLIT(C42,";")),0)</f>
@@ -22039,7 +22036,7 @@
         <v>341</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
@@ -22132,14 +22129,14 @@
         <v>1</v>
       </c>
       <c r="AJ42" s="71" t="str">
-        <f>MID(D42,5,LEN(D42)-4)</f>
+        <f t="shared" si="3"/>
         <v>ARAT1</v>
       </c>
     </row>
     <row r="43" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B43" cm="1">
         <f t="array" ref="B43">IFERROR(MAX(--_xlfn.TEXTSPLIT(C43,";")),0)</f>
@@ -22243,14 +22240,14 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="71" t="str">
-        <f>MID(D43,5,LEN(D43)-4)</f>
+        <f t="shared" si="3"/>
         <v>ARNO1</v>
       </c>
     </row>
     <row r="44" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B44" cm="1">
         <f t="array" ref="B44">IFERROR(MAX(--_xlfn.TEXTSPLIT(C44,";")),0)</f>
@@ -22356,14 +22353,14 @@
         <v>1</v>
       </c>
       <c r="AJ44" s="71" t="str">
-        <f>MID(D44,5,LEN(D44)-4)</f>
+        <f t="shared" si="3"/>
         <v>ATEP1</v>
       </c>
     </row>
     <row r="45" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B45" cm="1">
         <f t="array" ref="B45">IFERROR(MAX(--_xlfn.TEXTSPLIT(C45,";")),0)</f>
@@ -22469,14 +22466,14 @@
         <v>1</v>
       </c>
       <c r="AJ45" s="71" t="str">
-        <f>MID(D45,5,LEN(D45)-4)</f>
+        <f t="shared" si="3"/>
         <v>ATEP2</v>
       </c>
     </row>
     <row r="46" spans="1:36" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B46" cm="1">
         <f t="array" ref="B46">IFERROR(MAX(--_xlfn.TEXTSPLIT(C46,";")),0)</f>
@@ -22582,14 +22579,14 @@
         <v>1</v>
       </c>
       <c r="AJ46" s="71" t="str">
-        <f>MID(D46,5,LEN(D46)-4)</f>
+        <f t="shared" si="3"/>
         <v>ATEP3</v>
       </c>
     </row>
     <row r="47" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B47" cm="1">
         <f t="array" ref="B47">IFERROR(MAX(--_xlfn.TEXTSPLIT(C47,";")),0)</f>
@@ -22695,14 +22692,14 @@
         <v>1</v>
       </c>
       <c r="AJ47" s="71" t="str">
-        <f>MID(D47,5,LEN(D47)-4)</f>
+        <f t="shared" si="3"/>
         <v>ATEP4</v>
       </c>
     </row>
     <row r="48" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B48" cm="1">
         <f t="array" ref="B48">IFERROR(MAX(--_xlfn.TEXTSPLIT(C48,";")),0)</f>
@@ -22808,14 +22805,14 @@
         <v>0.55930000000000002</v>
       </c>
       <c r="AJ48" s="71" t="str">
-        <f>MID(D48,5,LEN(D48)-4)</f>
+        <f t="shared" si="3"/>
         <v>AVAM3</v>
       </c>
     </row>
     <row r="49" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B49" cm="1">
         <f t="array" ref="B49">IFERROR(MAX(--_xlfn.TEXTSPLIT(C49,";")),0)</f>
@@ -22921,14 +22918,14 @@
         <v>1</v>
       </c>
       <c r="AJ49" s="71" t="str">
-        <f>MID(D49,5,LEN(D49)-4)</f>
+        <f t="shared" si="3"/>
         <v>AVES1</v>
       </c>
     </row>
     <row r="50" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B50" cm="1">
         <f t="array" ref="B50">IFERROR(MAX(--_xlfn.TEXTSPLIT(C50,";")),0)</f>
@@ -23034,14 +23031,14 @@
         <v>1</v>
       </c>
       <c r="AJ50" s="71" t="str">
-        <f>MID(D50,5,LEN(D50)-4)</f>
+        <f t="shared" si="3"/>
         <v>AVNP1</v>
       </c>
     </row>
     <row r="51" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B51" cm="1">
         <f t="array" ref="B51">IFERROR(MAX(--_xlfn.TEXTSPLIT(C51,";")),0)</f>
@@ -23147,14 +23144,14 @@
         <v>1</v>
       </c>
       <c r="AJ51" s="71" t="str">
-        <f>MID(D51,5,LEN(D51)-4)</f>
+        <f t="shared" si="3"/>
         <v>CDMA1</v>
       </c>
     </row>
     <row r="52" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B52" cm="1">
         <f t="array" ref="B52">IFERROR(MAX(--_xlfn.TEXTSPLIT(C52,";")),0)</f>
@@ -23167,7 +23164,7 @@
         <v>156</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="F52" s="1">
         <v>1</v>
@@ -23260,14 +23257,14 @@
         <v>1</v>
       </c>
       <c r="AJ52" s="71" t="str">
-        <f>MID(D52,5,LEN(D52)-4)</f>
+        <f t="shared" si="3"/>
         <v>CHCO1</v>
       </c>
     </row>
     <row r="53" spans="1:36" ht="242.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B53" cm="1">
         <f t="array" ref="B53">IFERROR(MAX(--_xlfn.TEXTSPLIT(C53,";")),0)</f>
@@ -23280,7 +23277,7 @@
         <v>946</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="F53" s="1">
         <v>2</v>
@@ -23373,14 +23370,14 @@
         <v>0</v>
       </c>
       <c r="AJ53" s="71" t="str">
-        <f>MID(D53,5,LEN(D53)-4)</f>
+        <f t="shared" si="3"/>
         <v>CHCO2</v>
       </c>
     </row>
     <row r="54" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B54" cm="1">
         <f t="array" ref="B54">IFERROR(MAX(--_xlfn.TEXTSPLIT(C54,";")),0)</f>
@@ -23486,14 +23483,14 @@
         <v>1</v>
       </c>
       <c r="AJ54" s="71" t="str">
-        <f>MID(D54,5,LEN(D54)-4)</f>
+        <f t="shared" si="3"/>
         <v>CNPU1</v>
       </c>
     </row>
     <row r="55" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B55" cm="1">
         <f t="array" ref="B55">IFERROR(MAX(--_xlfn.TEXTSPLIT(C55,";")),0)</f>
@@ -23599,14 +23596,14 @@
         <v>1</v>
       </c>
       <c r="AJ55" s="71" t="str">
-        <f>MID(D55,5,LEN(D55)-4)</f>
+        <f t="shared" si="3"/>
         <v>CFLL1</v>
       </c>
     </row>
     <row r="56" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B56" cm="1">
         <f t="array" ref="B56">IFERROR(MAX(--_xlfn.TEXTSPLIT(C56,";")),0)</f>
@@ -23712,14 +23709,14 @@
         <v>736</v>
       </c>
       <c r="AJ56" s="71" t="str">
-        <f>MID(D56,5,LEN(D56)-4)</f>
+        <f t="shared" si="3"/>
         <v>CNPU2</v>
       </c>
     </row>
     <row r="57" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B57" cm="1">
         <f t="array" ref="B57">IFERROR(MAX(--_xlfn.TEXTSPLIT(C57,";")),0)</f>
@@ -23732,7 +23729,7 @@
         <v>600</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="F57" s="1">
         <v>1</v>
@@ -23825,14 +23822,14 @@
         <v>1</v>
       </c>
       <c r="AJ57" s="72" t="str">
-        <f>MID(D57,5,LEN(D57)-4)</f>
+        <f t="shared" si="3"/>
         <v>COCA1</v>
       </c>
     </row>
     <row r="58" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B58" cm="1">
         <f t="array" ref="B58">IFERROR(MAX(--_xlfn.TEXTSPLIT(C58,";")),0)</f>
@@ -23938,14 +23935,14 @@
         <v>1</v>
       </c>
       <c r="AJ58" s="71" t="str">
-        <f>MID(D58,5,LEN(D58)-4)</f>
+        <f t="shared" si="3"/>
         <v>CMVR1</v>
       </c>
     </row>
     <row r="59" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B59" cm="1">
         <f t="array" ref="B59">IFERROR(MAX(--_xlfn.TEXTSPLIT(C59,";")),0)</f>
@@ -23958,7 +23955,7 @@
         <v>213</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="F59" s="1">
         <v>1</v>
@@ -24051,14 +24048,14 @@
         <v>1</v>
       </c>
       <c r="AJ59" s="71" t="str">
-        <f>MID(D59,5,LEN(D59)-4)</f>
+        <f t="shared" si="3"/>
         <v>COTE1</v>
       </c>
     </row>
     <row r="60" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B60" cm="1">
         <f t="array" ref="B60">IFERROR(MAX(--_xlfn.TEXTSPLIT(C60,";")),0)</f>
@@ -24164,14 +24161,14 @@
         <v>1</v>
       </c>
       <c r="AJ60" s="71" t="str">
-        <f>MID(D60,5,LEN(D60)-4)</f>
+        <f t="shared" si="3"/>
         <v>ISVV1</v>
       </c>
     </row>
     <row r="61" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B61" cm="1">
         <f t="array" ref="B61">IFERROR(MAX(--_xlfn.TEXTSPLIT(C61,";")),0)</f>
@@ -24275,14 +24272,14 @@
         <v>0</v>
       </c>
       <c r="AJ61" s="71" t="str">
-        <f>MID(D61,5,LEN(D61)-4)</f>
+        <f t="shared" si="3"/>
         <v>ISVV2</v>
       </c>
     </row>
     <row r="62" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B62" cm="1">
         <f t="array" ref="B62">IFERROR(MAX(--_xlfn.TEXTSPLIT(C62,";")),0)</f>
@@ -24295,7 +24292,7 @@
         <v>172</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="F62" s="1">
         <v>1</v>
@@ -24388,14 +24385,14 @@
         <v>1</v>
       </c>
       <c r="AJ62" s="71" t="str">
-        <f>MID(D62,5,LEN(D62)-4)</f>
+        <f t="shared" si="3"/>
         <v>LVLS1</v>
       </c>
     </row>
     <row r="63" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B63" cm="1">
         <f t="array" ref="B63">IFERROR(MAX(--_xlfn.TEXTSPLIT(C63,";")),0)</f>
@@ -24501,14 +24498,14 @@
         <v>1</v>
       </c>
       <c r="AJ63" s="71" t="str">
-        <f>MID(D63,5,LEN(D63)-4)</f>
+        <f t="shared" si="3"/>
         <v>CSJS1</v>
       </c>
     </row>
     <row r="64" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B64" cm="1">
         <f t="array" ref="B64">IFERROR(MAX(--_xlfn.TEXTSPLIT(C64,";")),0)</f>
@@ -24614,14 +24611,14 @@
         <v>1</v>
       </c>
       <c r="AJ64" s="71" t="str">
-        <f>MID(D64,5,LEN(D64)-4)</f>
+        <f t="shared" si="3"/>
         <v>CTSR1</v>
       </c>
     </row>
     <row r="65" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <f t="shared" si="1"/>
-        <v>188</v>
+        <f t="shared" si="2"/>
+        <v>189</v>
       </c>
       <c r="B65" cm="1">
         <f t="array" ref="B65">IFERROR(MAX(--_xlfn.TEXTSPLIT(C65,";")),0)</f>
@@ -24727,14 +24724,14 @@
         <v>1</v>
       </c>
       <c r="AJ65" s="71" t="str">
-        <f>MID(D65,5,LEN(D65)-4)</f>
+        <f t="shared" si="3"/>
         <v>CVSR1</v>
       </c>
     </row>
     <row r="66" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <f t="shared" ref="A66:A97" si="2">MAX($B$2:$B$128)</f>
-        <v>188</v>
+        <f t="shared" ref="A66:A97" si="4">MAX($B$2:$B$128)</f>
+        <v>189</v>
       </c>
       <c r="B66" cm="1">
         <f t="array" ref="B66">IFERROR(MAX(--_xlfn.TEXTSPLIT(C66,";")),0)</f>
@@ -24747,7 +24744,7 @@
         <v>431</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="F66" s="1">
         <v>1</v>
@@ -24840,14 +24837,14 @@
         <v>1</v>
       </c>
       <c r="AJ66" s="71" t="str">
-        <f>MID(D66,5,LEN(D66)-4)</f>
+        <f t="shared" ref="AJ66:AJ97" si="5">MID(D66,5,LEN(D66)-4)</f>
         <v>ECVI1</v>
       </c>
     </row>
     <row r="67" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B67" cm="1">
         <f t="array" ref="B67">IFERROR(MAX(--_xlfn.TEXTSPLIT(C67,";")),0)</f>
@@ -24860,7 +24857,7 @@
         <v>261</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="F67" s="1">
         <v>1</v>
@@ -24953,14 +24950,14 @@
         <v>0</v>
       </c>
       <c r="AJ67" s="71" t="str">
-        <f>MID(D67,5,LEN(D67)-4)</f>
+        <f t="shared" si="5"/>
         <v>EEBA1</v>
       </c>
     </row>
     <row r="68" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B68" cm="1">
         <f t="array" ref="B68">IFERROR(MAX(--_xlfn.TEXTSPLIT(C68,";")),0)</f>
@@ -25066,14 +25063,14 @@
         <v>1</v>
       </c>
       <c r="AJ68" s="71" t="str">
-        <f>MID(D68,5,LEN(D68)-4)</f>
+        <f t="shared" si="5"/>
         <v>EIMC1</v>
       </c>
     </row>
     <row r="69" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B69" cm="1">
         <f t="array" ref="B69">IFERROR(MAX(--_xlfn.TEXTSPLIT(C69,";")),0)</f>
@@ -25086,7 +25083,7 @@
         <v>785</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="F69" s="1">
         <v>1</v>
@@ -25179,14 +25176,14 @@
         <v>0.21240000000000001</v>
       </c>
       <c r="AJ69" s="71" t="str">
-        <f>MID(D69,5,LEN(D69)-4)</f>
+        <f t="shared" si="5"/>
         <v>ELPA1</v>
       </c>
     </row>
     <row r="70" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B70" cm="1">
         <f t="array" ref="B70">IFERROR(MAX(--_xlfn.TEXTSPLIT(C70,";")),0)</f>
@@ -25199,7 +25196,7 @@
         <v>1026</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
@@ -25290,14 +25287,14 @@
         <v>0</v>
       </c>
       <c r="AJ70" s="71" t="str">
-        <f>MID(D70,5,LEN(D70)-4)</f>
+        <f t="shared" si="5"/>
         <v>EPCO1</v>
       </c>
     </row>
     <row r="71" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B71" cm="1">
         <f t="array" ref="B71">IFERROR(MAX(--_xlfn.TEXTSPLIT(C71,";")),0)</f>
@@ -25310,7 +25307,7 @@
         <v>714</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>
@@ -25403,14 +25400,14 @@
         <v>0</v>
       </c>
       <c r="AJ71" s="71" t="str">
-        <f>MID(D71,5,LEN(D71)-4)</f>
+        <f t="shared" si="5"/>
         <v>EPUN1</v>
       </c>
     </row>
     <row r="72" spans="1:36" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B72" cm="1">
         <f t="array" ref="B72">IFERROR(MAX(--_xlfn.TEXTSPLIT(C72,";")),0)</f>
@@ -25516,14 +25513,14 @@
         <v>1</v>
       </c>
       <c r="AJ72" s="71" t="str">
-        <f>MID(D72,5,LEN(D72)-4)</f>
+        <f t="shared" si="5"/>
         <v>ETPO1</v>
       </c>
     </row>
     <row r="73" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B73" cm="1">
         <f t="array" ref="B73">IFERROR(MAX(--_xlfn.TEXTSPLIT(C73,";")),0)</f>
@@ -25629,14 +25626,14 @@
         <v>1</v>
       </c>
       <c r="AJ73" s="71" t="str">
-        <f>MID(D73,5,LEN(D73)-4)</f>
+        <f t="shared" si="5"/>
         <v>ETTT1</v>
       </c>
     </row>
     <row r="74" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B74" cm="1">
         <f t="array" ref="B74">IFERROR(MAX(--_xlfn.TEXTSPLIT(C74,";")),0)</f>
@@ -25649,7 +25646,7 @@
         <v>872</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="F74" s="1">
         <v>1</v>
@@ -25742,14 +25739,14 @@
         <v>0.82579999999999998</v>
       </c>
       <c r="AJ74" s="71" t="str">
-        <f>MID(D74,5,LEN(D74)-4)</f>
+        <f t="shared" si="5"/>
         <v>HBUP1</v>
       </c>
     </row>
     <row r="75" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B75" cm="1">
         <f t="array" ref="B75">IFERROR(MAX(--_xlfn.TEXTSPLIT(C75,";")),0)</f>
@@ -25855,14 +25852,14 @@
         <v>0</v>
       </c>
       <c r="AJ75" s="71" t="str">
-        <f>MID(D75,5,LEN(D75)-4)</f>
+        <f t="shared" si="5"/>
         <v>HINN1</v>
       </c>
     </row>
     <row r="76" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B76" cm="1">
         <f t="array" ref="B76">IFERROR(MAX(--_xlfn.TEXTSPLIT(C76,";")),0)</f>
@@ -25875,7 +25872,7 @@
         <v>879</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="F76" s="1">
         <v>1</v>
@@ -25968,14 +25965,14 @@
         <v>886</v>
       </c>
       <c r="AJ76" s="71" t="str">
-        <f>MID(D76,5,LEN(D76)-4)</f>
+        <f t="shared" si="5"/>
         <v>HRBB1</v>
       </c>
     </row>
     <row r="77" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B77" cm="1">
         <f t="array" ref="B77">IFERROR(MAX(--_xlfn.TEXTSPLIT(C77,";")),0)</f>
@@ -25988,7 +25985,7 @@
         <v>863</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="F77" s="1">
         <v>1</v>
@@ -26081,14 +26078,14 @@
         <v>871</v>
       </c>
       <c r="AJ77" s="71" t="str">
-        <f>MID(D77,5,LEN(D77)-4)</f>
+        <f t="shared" si="5"/>
         <v>HRMA1</v>
       </c>
     </row>
     <row r="78" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B78" cm="1">
         <f t="array" ref="B78">IFERROR(MAX(--_xlfn.TEXTSPLIT(C78,";")),0)</f>
@@ -26101,7 +26098,7 @@
         <v>939</v>
       </c>
       <c r="E78" s="59" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="F78" s="1">
         <v>1</v>
@@ -26192,14 +26189,14 @@
         <v>0</v>
       </c>
       <c r="AJ78" s="71" t="str">
-        <f>MID(D78,5,LEN(D78)-4)</f>
+        <f t="shared" si="5"/>
         <v>HROG1</v>
       </c>
     </row>
     <row r="79" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B79" cm="1">
         <f t="array" ref="B79">IFERROR(MAX(--_xlfn.TEXTSPLIT(C79,";")),0)</f>
@@ -26212,7 +26209,7 @@
         <v>917</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="F79" s="1">
         <v>1</v>
@@ -26305,14 +26302,14 @@
         <v>0.2389</v>
       </c>
       <c r="AJ79" s="71" t="str">
-        <f>MID(D79,5,LEN(D79)-4)</f>
+        <f t="shared" si="5"/>
         <v>HRQQ1</v>
       </c>
     </row>
     <row r="80" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B80" cm="1">
         <f t="array" ref="B80">IFERROR(MAX(--_xlfn.TEXTSPLIT(C80,";")),0)</f>
@@ -26325,7 +26322,7 @@
         <v>902</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="F80" s="1">
         <v>1</v>
@@ -26418,14 +26415,14 @@
         <v>0.14749999999999999</v>
       </c>
       <c r="AJ80" s="71" t="str">
-        <f>MID(D80,5,LEN(D80)-4)</f>
+        <f t="shared" si="5"/>
         <v>HRQS1</v>
       </c>
     </row>
     <row r="81" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B81" cm="1">
         <f t="array" ref="B81">IFERROR(MAX(--_xlfn.TEXTSPLIT(C81,";")),0)</f>
@@ -26438,7 +26435,7 @@
         <v>887</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="F81" s="1">
         <v>1</v>
@@ -26531,14 +26528,14 @@
         <v>894</v>
       </c>
       <c r="AJ81" s="71" t="str">
-        <f>MID(D81,5,LEN(D81)-4)</f>
+        <f t="shared" si="5"/>
         <v>HRRL1</v>
       </c>
     </row>
     <row r="82" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B82" cm="1">
         <f t="array" ref="B82">IFERROR(MAX(--_xlfn.TEXTSPLIT(C82,";")),0)</f>
@@ -26644,14 +26641,14 @@
         <v>1</v>
       </c>
       <c r="AJ82" s="71" t="str">
-        <f>MID(D82,5,LEN(D82)-4)</f>
+        <f t="shared" si="5"/>
         <v>HSAN1</v>
       </c>
     </row>
     <row r="83" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B83" cm="1">
         <f t="array" ref="B83">IFERROR(MAX(--_xlfn.TEXTSPLIT(C83,";")),0)</f>
@@ -26757,14 +26754,14 @@
         <v>1</v>
       </c>
       <c r="AJ83" s="71" t="str">
-        <f>MID(D83,5,LEN(D83)-4)</f>
+        <f t="shared" si="5"/>
         <v>HSFB1</v>
       </c>
     </row>
     <row r="84" spans="1:36" ht="223.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B84" cm="1">
         <f t="array" ref="B84">IFERROR(MAX(--_xlfn.TEXTSPLIT(C84,";")),0)</f>
@@ -26870,14 +26867,14 @@
         <v>1</v>
       </c>
       <c r="AJ84" s="71" t="str">
-        <f>MID(D84,5,LEN(D84)-4)</f>
+        <f t="shared" si="5"/>
         <v>HSMF1</v>
       </c>
     </row>
     <row r="85" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B85" cm="1">
         <f t="array" ref="B85">IFERROR(MAX(--_xlfn.TEXTSPLIT(C85,";")),0)</f>
@@ -26983,14 +26980,14 @@
         <v>0.92200000000000004</v>
       </c>
       <c r="AJ85" s="71" t="str">
-        <f>MID(D85,5,LEN(D85)-4)</f>
+        <f t="shared" si="5"/>
         <v>HSSG1</v>
       </c>
     </row>
     <row r="86" spans="1:36" ht="148.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B86" cm="1">
         <f t="array" ref="B86">IFERROR(MAX(--_xlfn.TEXTSPLIT(C86,";")),0)</f>
@@ -27003,7 +27000,7 @@
         <v>932</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="F86" s="1">
         <v>1</v>
@@ -27096,14 +27093,14 @@
         <v>0</v>
       </c>
       <c r="AJ86" s="72" t="str">
-        <f>MID(D86,5,LEN(D86)-4)</f>
+        <f t="shared" si="5"/>
         <v>INAC1</v>
       </c>
     </row>
     <row r="87" spans="1:36" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B87" cm="1">
         <f t="array" ref="B87">IFERROR(MAX(--_xlfn.TEXTSPLIT(C87,";")),0)</f>
@@ -27116,7 +27113,7 @@
         <v>824</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="F87" s="1">
         <v>2</v>
@@ -27209,14 +27206,14 @@
         <v>831</v>
       </c>
       <c r="AJ87" s="1" t="str">
-        <f>MID(D87,5,LEN(D87)-4)</f>
+        <f t="shared" si="5"/>
         <v>LVLS2</v>
       </c>
     </row>
     <row r="88" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B88" cm="1">
         <f t="array" ref="B88">IFERROR(MAX(--_xlfn.TEXTSPLIT(C88,";")),0)</f>
@@ -27229,7 +27226,7 @@
         <v>658</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="F88" s="1">
         <v>1</v>
@@ -27322,14 +27319,14 @@
         <v>0.93169999999999997</v>
       </c>
       <c r="AJ88" s="71" t="str">
-        <f>MID(D88,5,LEN(D88)-4)</f>
+        <f t="shared" si="5"/>
         <v>NPIB1</v>
       </c>
     </row>
     <row r="89" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B89" cm="1">
         <f t="array" ref="B89">IFERROR(MAX(--_xlfn.TEXTSPLIT(C89,";")),0)</f>
@@ -27435,14 +27432,14 @@
         <v>0</v>
       </c>
       <c r="AJ89" s="71" t="str">
-        <f>MID(D89,5,LEN(D89)-4)</f>
+        <f t="shared" si="5"/>
         <v>ORSS1</v>
       </c>
     </row>
     <row r="90" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B90" cm="1">
         <f t="array" ref="B90">IFERROR(MAX(--_xlfn.TEXTSPLIT(C90,";")),0)</f>
@@ -27548,14 +27545,14 @@
         <v>1</v>
       </c>
       <c r="AJ90" s="71" t="str">
-        <f>MID(D90,5,LEN(D90)-4)</f>
+        <f t="shared" si="5"/>
         <v>NARA1</v>
       </c>
     </row>
     <row r="91" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B91" cm="1">
         <f t="array" ref="B91">IFERROR(MAX(--_xlfn.TEXTSPLIT(C91,";")),0)</f>
@@ -27659,14 +27656,14 @@
         <v>0</v>
       </c>
       <c r="AJ91" s="1" t="str">
-        <f>MID(D91,5,LEN(D91)-4)</f>
+        <f t="shared" si="5"/>
         <v>NARA2</v>
       </c>
     </row>
     <row r="92" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B92" cm="1">
         <f t="array" ref="B92">IFERROR(MAX(--_xlfn.TEXTSPLIT(C92,";")),0)</f>
@@ -27679,7 +27676,7 @@
         <v>547</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="F92" s="1">
         <v>1</v>
@@ -27772,14 +27769,14 @@
         <v>1</v>
       </c>
       <c r="AJ92" s="71" t="str">
-        <f>MID(D92,5,LEN(D92)-4)</f>
+        <f t="shared" si="5"/>
         <v>PMPA1</v>
       </c>
     </row>
     <row r="93" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B93" cm="1">
         <f t="array" ref="B93">IFERROR(MAX(--_xlfn.TEXTSPLIT(C93,";")),0)</f>
@@ -27792,7 +27789,7 @@
         <v>195</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="F93" s="1">
         <v>1</v>
@@ -27885,14 +27882,14 @@
         <v>1</v>
       </c>
       <c r="AJ93" s="72" t="str">
-        <f>MID(D93,5,LEN(D93)-4)</f>
+        <f t="shared" si="5"/>
         <v>RBPM1</v>
       </c>
     </row>
     <row r="94" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B94" cm="1">
         <f t="array" ref="B94">IFERROR(MAX(--_xlfn.TEXTSPLIT(C94,";")),0)</f>
@@ -27905,7 +27902,7 @@
         <v>1746</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="F94" s="59"/>
       <c r="G94" s="62" t="s">
@@ -27944,14 +27941,14 @@
       <c r="AH94" s="22"/>
       <c r="AI94" s="23"/>
       <c r="AJ94" s="1" t="str">
-        <f>MID(D94,5,LEN(D94)-4)</f>
+        <f t="shared" si="5"/>
         <v>RBPM2</v>
       </c>
     </row>
     <row r="95" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B95" cm="1">
         <f t="array" ref="B95">IFERROR(MAX(--_xlfn.TEXTSPLIT(C95,";")),0)</f>
@@ -28057,14 +28054,14 @@
         <v>1</v>
       </c>
       <c r="AJ95" s="1" t="str">
-        <f>MID(D95,5,LEN(D95)-4)</f>
+        <f t="shared" si="5"/>
         <v>PCIS1</v>
       </c>
     </row>
     <row r="96" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B96" cm="1">
         <f t="array" ref="B96">IFERROR(MAX(--_xlfn.TEXTSPLIT(C96,";")),0)</f>
@@ -28170,14 +28167,14 @@
         <v>1</v>
       </c>
       <c r="AJ96" s="1" t="str">
-        <f>MID(D96,5,LEN(D96)-4)</f>
+        <f t="shared" si="5"/>
         <v>RITP1</v>
       </c>
     </row>
     <row r="97" spans="1:36" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
-        <f t="shared" si="2"/>
-        <v>188</v>
+        <f t="shared" si="4"/>
+        <v>189</v>
       </c>
       <c r="B97" cm="1">
         <f t="array" ref="B97">IFERROR(MAX(--_xlfn.TEXTSPLIT(C97,";")),0)</f>
@@ -28283,14 +28280,14 @@
         <v>1</v>
       </c>
       <c r="AJ97" s="71" t="str">
-        <f>MID(D97,5,LEN(D97)-4)</f>
+        <f t="shared" si="5"/>
         <v>PP1G1</v>
       </c>
     </row>
     <row r="98" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <f t="shared" ref="A98:A128" si="3">MAX($B$2:$B$128)</f>
-        <v>188</v>
+        <f t="shared" ref="A98:A128" si="6">MAX($B$2:$B$128)</f>
+        <v>189</v>
       </c>
       <c r="B98" cm="1">
         <f t="array" ref="B98">IFERROR(MAX(--_xlfn.TEXTSPLIT(C98,";")),0)</f>
@@ -28396,14 +28393,14 @@
         <v>0</v>
       </c>
       <c r="AJ98" s="71" t="str">
-        <f>MID(D98,5,LEN(D98)-4)</f>
+        <f t="shared" ref="AJ98:AJ128" si="7">MID(D98,5,LEN(D98)-4)</f>
         <v>PP2G1</v>
       </c>
     </row>
     <row r="99" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B99" cm="1">
         <f t="array" ref="B99">IFERROR(MAX(--_xlfn.TEXTSPLIT(C99,";")),0)</f>
@@ -28509,14 +28506,14 @@
         <v>1</v>
       </c>
       <c r="AJ99" s="71" t="str">
-        <f>MID(D99,5,LEN(D99)-4)</f>
+        <f t="shared" si="7"/>
         <v>PP2G2</v>
       </c>
     </row>
     <row r="100" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B100" cm="1">
         <f t="array" ref="B100">IFERROR(MAX(--_xlfn.TEXTSPLIT(C100,";")),0)</f>
@@ -28529,7 +28526,7 @@
         <v>372</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="F100" s="1">
         <v>1</v>
@@ -28622,14 +28619,14 @@
         <v>1</v>
       </c>
       <c r="AJ100" s="71" t="str">
-        <f>MID(D100,5,LEN(D100)-4)</f>
+        <f t="shared" si="7"/>
         <v>PP3G1</v>
       </c>
     </row>
     <row r="101" spans="1:36" ht="168.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B101" cm="1">
         <f t="array" ref="B101">IFERROR(MAX(--_xlfn.TEXTSPLIT(C101,";")),0)</f>
@@ -28733,14 +28730,14 @@
         <v>269</v>
       </c>
       <c r="AJ101" s="71" t="str">
-        <f>MID(D101,5,LEN(D101)-4)</f>
+        <f t="shared" si="7"/>
         <v>PP4T1</v>
       </c>
     </row>
     <row r="102" spans="1:36" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B102" cm="1">
         <f t="array" ref="B102">IFERROR(MAX(--_xlfn.TEXTSPLIT(C102,";")),0)</f>
@@ -28846,14 +28843,14 @@
         <v>1</v>
       </c>
       <c r="AJ102" s="1" t="str">
-        <f>MID(D102,5,LEN(D102)-4)</f>
+        <f t="shared" si="7"/>
         <v>PTLA1</v>
       </c>
     </row>
     <row r="103" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B103" cm="1">
         <f t="array" ref="B103">IFERROR(MAX(--_xlfn.TEXTSPLIT(C103,";")),0)</f>
@@ -28866,7 +28863,7 @@
         <v>839</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="F103" s="1">
         <v>1</v>
@@ -28959,14 +28956,14 @@
         <v>847</v>
       </c>
       <c r="AJ103" s="1" t="str">
-        <f>MID(D103,5,LEN(D103)-4)</f>
+        <f t="shared" si="7"/>
         <v>RAUS1</v>
       </c>
     </row>
     <row r="104" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B104" cm="1">
         <f t="array" ref="B104">IFERROR(MAX(--_xlfn.TEXTSPLIT(C104,";")),0)</f>
@@ -28979,7 +28976,7 @@
         <v>630</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="F104" s="1">
         <v>1</v>
@@ -29072,14 +29069,14 @@
         <v>0</v>
       </c>
       <c r="AJ104" s="71" t="str">
-        <f>MID(D104,5,LEN(D104)-4)</f>
+        <f t="shared" si="7"/>
         <v>RLOA1</v>
       </c>
     </row>
     <row r="105" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B105" cm="1">
         <f t="array" ref="B105">IFERROR(MAX(--_xlfn.TEXTSPLIT(C105,";")),0)</f>
@@ -29092,7 +29089,7 @@
         <v>770</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="F105" s="1">
         <v>2</v>
@@ -29183,14 +29180,14 @@
         <v>777</v>
       </c>
       <c r="AJ105" s="71" t="str">
-        <f>MID(D105,5,LEN(D105)-4)</f>
+        <f t="shared" si="7"/>
         <v>RLOA2</v>
       </c>
     </row>
     <row r="106" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B106" cm="1">
         <f t="array" ref="B106">IFERROR(MAX(--_xlfn.TEXTSPLIT(C106,";")),0)</f>
@@ -29296,14 +29293,14 @@
         <v>769</v>
       </c>
       <c r="AJ106" s="71" t="str">
-        <f>MID(D106,5,LEN(D106)-4)</f>
+        <f t="shared" si="7"/>
         <v>RNAH1</v>
       </c>
     </row>
     <row r="107" spans="1:36" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B107" cm="1">
         <f t="array" ref="B107">IFERROR(MAX(--_xlfn.TEXTSPLIT(C107,";")),0)</f>
@@ -29313,7 +29310,7 @@
         <v>1830</v>
       </c>
       <c r="D107" s="58" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="E107" s="62" t="s">
         <v>1736</v>
@@ -29359,14 +29356,14 @@
       <c r="AH107" s="22"/>
       <c r="AI107" s="27"/>
       <c r="AJ107" s="71" t="str">
-        <f>MID(D107,5,LEN(D107)-4)</f>
+        <f t="shared" si="7"/>
         <v>RPMO1</v>
       </c>
     </row>
     <row r="108" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B108" cm="1">
         <f t="array" ref="B108">IFERROR(MAX(--_xlfn.TEXTSPLIT(C108,";")),0)</f>
@@ -29418,14 +29415,14 @@
       <c r="AH108" s="22"/>
       <c r="AI108" s="23"/>
       <c r="AJ108" s="71" t="str">
-        <f>MID(D108,5,LEN(D108)-4)</f>
+        <f t="shared" si="7"/>
         <v>RTCC</v>
       </c>
     </row>
     <row r="109" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B109" cm="1">
         <f t="array" ref="B109">IFERROR(MAX(--_xlfn.TEXTSPLIT(C109,";")),0)</f>
@@ -29531,14 +29528,14 @@
         <v>1</v>
       </c>
       <c r="AJ109" s="71" t="str">
-        <f>MID(D109,5,LEN(D109)-4)</f>
+        <f t="shared" si="7"/>
         <v>RVLC1</v>
       </c>
     </row>
     <row r="110" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B110" cm="1">
         <f t="array" ref="B110">IFERROR(MAX(--_xlfn.TEXTSPLIT(C110,";")),0)</f>
@@ -29551,7 +29548,7 @@
         <v>138</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
@@ -29644,14 +29641,14 @@
         <v>1</v>
       </c>
       <c r="AJ110" s="71" t="str">
-        <f>MID(D110,5,LEN(D110)-4)</f>
+        <f t="shared" si="7"/>
         <v>SALV1</v>
       </c>
     </row>
     <row r="111" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B111" cm="1">
         <f t="array" ref="B111">IFERROR(MAX(--_xlfn.TEXTSPLIT(C111,";")),0)</f>
@@ -29664,7 +29661,7 @@
         <v>977</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="F111" s="1">
         <v>2</v>
@@ -29755,14 +29752,14 @@
         <v>0</v>
       </c>
       <c r="AJ111" s="71" t="str">
-        <f>MID(D111,5,LEN(D111)-4)</f>
+        <f t="shared" si="7"/>
         <v>SALV2</v>
       </c>
     </row>
     <row r="112" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B112" cm="1">
         <f t="array" ref="B112">IFERROR(MAX(--_xlfn.TEXTSPLIT(C112,";")),0)</f>
@@ -29868,14 +29865,14 @@
         <v>1</v>
       </c>
       <c r="AJ112" s="71" t="str">
-        <f>MID(D112,5,LEN(D112)-4)</f>
+        <f t="shared" si="7"/>
         <v>SASA1</v>
       </c>
     </row>
     <row r="113" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B113" cm="1">
         <f t="array" ref="B113">IFERROR(MAX(--_xlfn.TEXTSPLIT(C113,";")),0)</f>
@@ -29981,14 +29978,14 @@
         <v>0</v>
       </c>
       <c r="AJ113" s="71" t="str">
-        <f>MID(D113,5,LEN(D113)-4)</f>
+        <f t="shared" si="7"/>
         <v>SASA2</v>
       </c>
     </row>
     <row r="114" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B114" cm="1">
         <f t="array" ref="B114">IFERROR(MAX(--_xlfn.TEXTSPLIT(C114,";")),0)</f>
@@ -30001,7 +29998,7 @@
         <v>221</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="F114" s="1">
         <v>1</v>
@@ -30094,14 +30091,14 @@
         <v>1</v>
       </c>
       <c r="AJ114" s="71" t="str">
-        <f>MID(D114,5,LEN(D114)-4)</f>
+        <f t="shared" si="7"/>
         <v>SATA1</v>
       </c>
     </row>
     <row r="115" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B115" cm="1">
         <f t="array" ref="B115">IFERROR(MAX(--_xlfn.TEXTSPLIT(C115,";")),0)</f>
@@ -30207,14 +30204,14 @@
         <v>1</v>
       </c>
       <c r="AJ115" s="71" t="str">
-        <f>MID(D115,5,LEN(D115)-4)</f>
+        <f t="shared" si="7"/>
         <v>SCLA1</v>
       </c>
     </row>
     <row r="116" spans="1:36" ht="132.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B116" cm="1">
         <f t="array" ref="B116">IFERROR(MAX(--_xlfn.TEXTSPLIT(C116,";")),0)</f>
@@ -30320,14 +30317,14 @@
         <v>1</v>
       </c>
       <c r="AJ116" s="71" t="str">
-        <f>MID(D116,5,LEN(D116)-4)</f>
+        <f t="shared" si="7"/>
         <v>SNSS1</v>
       </c>
     </row>
     <row r="117" spans="1:36" ht="155.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B117" cm="1">
         <f t="array" ref="B117">IFERROR(MAX(--_xlfn.TEXTSPLIT(C117,";")),0)</f>
@@ -30340,7 +30337,7 @@
         <v>244</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="F117" s="1">
         <v>1</v>
@@ -30433,14 +30430,14 @@
         <v>1</v>
       </c>
       <c r="AJ117" s="71" t="str">
-        <f>MID(D117,5,LEN(D117)-4)</f>
+        <f t="shared" si="7"/>
         <v>SOPN1</v>
       </c>
     </row>
     <row r="118" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B118" cm="1">
         <f t="array" ref="B118">IFERROR(MAX(--_xlfn.TEXTSPLIT(C118,";")),0)</f>
@@ -30453,7 +30450,7 @@
         <v>118</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="F118" s="1">
         <v>1</v>
@@ -30546,14 +30543,14 @@
         <v>1</v>
       </c>
       <c r="AJ118" s="71" t="str">
-        <f>MID(D118,5,LEN(D118)-4)</f>
+        <f t="shared" si="7"/>
         <v>TACH1</v>
       </c>
     </row>
     <row r="119" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B119" cm="1">
         <f t="array" ref="B119">IFERROR(MAX(--_xlfn.TEXTSPLIT(C119,";")),0)</f>
@@ -30566,7 +30563,7 @@
         <v>848</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="F119" s="1">
         <v>2</v>
@@ -30659,14 +30656,14 @@
         <v>0</v>
       </c>
       <c r="AJ119" s="71" t="str">
-        <f>MID(D119,5,LEN(D119)-4)</f>
+        <f t="shared" si="7"/>
         <v>TACH2</v>
       </c>
     </row>
     <row r="120" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B120" cm="1">
         <f t="array" ref="B120">IFERROR(MAX(--_xlfn.TEXTSPLIT(C120,";")),0)</f>
@@ -30679,7 +30676,7 @@
         <v>778</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
@@ -30772,21 +30769,21 @@
         <v>0.57709999999999995</v>
       </c>
       <c r="AJ120" s="71" t="str">
-        <f>MID(D120,5,LEN(D120)-4)</f>
+        <f t="shared" si="7"/>
         <v>TELB1</v>
       </c>
     </row>
     <row r="121" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B121" cm="1">
         <f t="array" ref="B121">IFERROR(MAX(--_xlfn.TEXTSPLIT(C121,";")),0)</f>
-        <v>161</v>
-      </c>
-      <c r="C121" t="s">
-        <v>1841</v>
+        <v>189</v>
+      </c>
+      <c r="C121">
+        <v>189</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>32</v>
@@ -30885,21 +30882,21 @@
         <v>1</v>
       </c>
       <c r="AJ121" s="71" t="str">
-        <f>MID(D121,5,LEN(D121)-4)</f>
+        <f t="shared" si="7"/>
         <v>TEME1</v>
       </c>
     </row>
     <row r="122" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B122" cm="1">
         <f t="array" ref="B122">IFERROR(MAX(--_xlfn.TEXTSPLIT(C122,";")),0)</f>
-        <v>161</v>
-      </c>
-      <c r="C122" t="s">
-        <v>1841</v>
+        <v>161.18899999999999</v>
+      </c>
+      <c r="C122">
+        <v>161.18899999999999</v>
       </c>
       <c r="D122" s="21" t="s">
         <v>722</v>
@@ -30998,27 +30995,27 @@
         <v>1</v>
       </c>
       <c r="AJ122" s="71" t="str">
-        <f>MID(D122,5,LEN(D122)-4)</f>
+        <f t="shared" si="7"/>
         <v>TEME2</v>
       </c>
     </row>
     <row r="123" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B123" cm="1">
         <f t="array" ref="B123">IFERROR(MAX(--_xlfn.TEXTSPLIT(C123,";")),0)</f>
         <v>162</v>
       </c>
       <c r="C123" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="D123" s="21" t="s">
         <v>164</v>
       </c>
       <c r="E123" s="21" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="F123" s="1">
         <v>1</v>
@@ -31111,33 +31108,33 @@
         <v>1</v>
       </c>
       <c r="AJ123" s="71" t="str">
-        <f>MID(D123,5,LEN(D123)-4)</f>
+        <f t="shared" si="7"/>
         <v>TERB1</v>
       </c>
     </row>
     <row r="124" spans="1:36" ht="118.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B124" cm="1">
         <f t="array" ref="B124">IFERROR(MAX(--_xlfn.TEXTSPLIT(C124,";")),0)</f>
         <v>162</v>
       </c>
       <c r="C124" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="D124" s="29" t="s">
         <v>1017</v>
       </c>
       <c r="E124" s="21" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="F124" s="1">
         <v>2</v>
       </c>
       <c r="G124" s="29" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>1019</v>
@@ -31222,27 +31219,27 @@
         <v>0</v>
       </c>
       <c r="AJ124" s="71" t="str">
-        <f>MID(D124,5,LEN(D124)-4)</f>
+        <f t="shared" si="7"/>
         <v>TERB2</v>
       </c>
     </row>
     <row r="125" spans="1:36" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B125" cm="1">
         <f t="array" ref="B125">IFERROR(MAX(--_xlfn.TEXTSPLIT(C125,";")),0)</f>
         <v>163</v>
       </c>
       <c r="C125" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="D125" s="11" t="s">
         <v>622</v>
       </c>
       <c r="E125" s="63" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="F125" s="1">
         <v>1</v>
@@ -31335,21 +31332,21 @@
         <v>1</v>
       </c>
       <c r="AJ125" s="71" t="str">
-        <f>MID(D125,5,LEN(D125)-4)</f>
+        <f t="shared" si="7"/>
         <v>VALS1</v>
       </c>
     </row>
     <row r="126" spans="1:36" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B126" cm="1">
         <f t="array" ref="B126">IFERROR(MAX(--_xlfn.TEXTSPLIT(C126,";")),0)</f>
         <v>164</v>
       </c>
       <c r="C126" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>296</v>
@@ -31448,27 +31445,27 @@
         <v>1</v>
       </c>
       <c r="AJ126" s="71" t="str">
-        <f>MID(D126,5,LEN(D126)-4)</f>
+        <f t="shared" si="7"/>
         <v>VAME1</v>
       </c>
     </row>
     <row r="127" spans="1:36" ht="125.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B127" cm="1">
         <f t="array" ref="B127">IFERROR(MAX(--_xlfn.TEXTSPLIT(C127,";")),0)</f>
         <v>168</v>
       </c>
       <c r="C127" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="D127" s="11" t="s">
         <v>508</v>
       </c>
       <c r="E127" s="63" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="F127" s="1">
         <v>1</v>
@@ -31561,21 +31558,21 @@
         <v>1</v>
       </c>
       <c r="AJ127" s="71" t="str">
-        <f>MID(D127,5,LEN(D127)-4)</f>
+        <f t="shared" si="7"/>
         <v>VCAL1</v>
       </c>
     </row>
     <row r="128" spans="1:36" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
-        <f t="shared" si="3"/>
-        <v>188</v>
+        <f t="shared" si="6"/>
+        <v>189</v>
       </c>
       <c r="B128" cm="1">
         <f t="array" ref="B128">IFERROR(MAX(--_xlfn.TEXTSPLIT(C128,";")),0)</f>
         <v>174</v>
       </c>
       <c r="C128" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>447</v>
@@ -31674,7 +31671,7 @@
         <v>1</v>
       </c>
       <c r="AJ128" s="71" t="str">
-        <f>MID(D128,5,LEN(D128)-4)</f>
+        <f t="shared" si="7"/>
         <v>VVSK1</v>
       </c>
     </row>
